--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{476FAA6E-4A43-486A-96BC-36DC1A9A96BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB6F5132-8072-4801-B56E-FC019376AE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F262961D-661A-452B-9CD8-53CBA1DF8108}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C85A1A-DA8C-4B76-AFF9-D9C7DB908623}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58ED8727-A259-4902-874B-0D907DEB8DEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB5F2E6-8C6D-4B22-92F6-867BD0E84406}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB6F5132-8072-4801-B56E-FC019376AE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BE1F72-F9AE-427A-9F8D-4209DB08972F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C85A1A-DA8C-4B76-AFF9-D9C7DB908623}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2AE1689-B642-40AA-9FE7-48802535F9DF}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB5F2E6-8C6D-4B22-92F6-867BD0E84406}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E016E9C-581B-4CC3-A3A9-145E2E59D741}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BE1F72-F9AE-427A-9F8D-4209DB08972F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{581D2D7C-0497-4452-8F05-9C7C0827AB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2AE1689-B642-40AA-9FE7-48802535F9DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9FAC3FF-16D3-4DDB-84C6-3E947B463AD6}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E016E9C-581B-4CC3-A3A9-145E2E59D741}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABC8EB3-0FF5-43FB-8561-CD63D92B6068}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{581D2D7C-0497-4452-8F05-9C7C0827AB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AAAC928-AA5F-4E18-828B-06B7E1CF307B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9FAC3FF-16D3-4DDB-84C6-3E947B463AD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D845FEB-6EB1-4C32-8B25-4DED5ABD4753}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABC8EB3-0FF5-43FB-8561-CD63D92B6068}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2BB182-29BB-42C8-A186-EED3454A250B}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AAAC928-AA5F-4E18-828B-06B7E1CF307B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A41806B-9BF9-405B-81CE-64C57630F088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D845FEB-6EB1-4C32-8B25-4DED5ABD4753}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88838907-D4D4-42FB-8DCC-492B24DCC945}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2BB182-29BB-42C8-A186-EED3454A250B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2AFE1B-3583-4B2A-8CD0-52E4804EF636}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A41806B-9BF9-405B-81CE-64C57630F088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51F1CB5-7BC9-4291-BAD6-D0101921FCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88838907-D4D4-42FB-8DCC-492B24DCC945}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79958115-37FF-4384-BA4A-35B24D46D90F}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2AFE1B-3583-4B2A-8CD0-52E4804EF636}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6312EDCC-7B84-4AD2-A090-3396B7E67C57}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51F1CB5-7BC9-4291-BAD6-D0101921FCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40B0A2C6-DD51-496F-A86B-581C84C4E118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79958115-37FF-4384-BA4A-35B24D46D90F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F02AC37-1612-4EF7-AF8A-8686A4A91C71}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6312EDCC-7B84-4AD2-A090-3396B7E67C57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB22317-7C2C-48B1-9066-6EF8EF7FF53A}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40B0A2C6-DD51-496F-A86B-581C84C4E118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68C07DBF-A432-4CEB-BC01-F86DD0A97F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F02AC37-1612-4EF7-AF8A-8686A4A91C71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47177EFC-52C0-488D-AC8A-C6559EC4E71A}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB22317-7C2C-48B1-9066-6EF8EF7FF53A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE04DE1D-8DEF-4FFF-B83D-74EE775DB0F8}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IDN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68C07DBF-A432-4CEB-BC01-F86DD0A97F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0220E9BC-7076-4EDC-B37D-0630C4D6A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -4156,7 +4156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47177EFC-52C0-488D-AC8A-C6559EC4E71A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78BB5066-984D-4421-9A52-B9B63EE1F851}">
   <dimension ref="B2:AF792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18003,7 +18003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE04DE1D-8DEF-4FFF-B83D-74EE775DB0F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDB7D8C-9CE1-4146-8745-22359B39DE85}">
   <dimension ref="B9:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
